--- a/paper/source_data/ed4_source_data.xlsx
+++ b/paper/source_data/ed4_source_data.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Extended Data Fig. 5 | Linear and raw-feature comparators for blood count completion.** **a**, Mean absolute error (MAE) relative to the training median, whole panel hidden. **b**, BRAN without retina minus Ridge MAE, as a percentage of median MAE. **c**, Haemoglobin MAE below 12 g/dL and paired differences. **d**, Macro AUROC over 25 conditions for one classifier given each arm's estimates, and prespecified paired differences (Bonferroni). **e**, BRAN minus ridge models given its inputs plus 64 retinal components. **f**, AUROC for haemoglobin below 12 g/dL beside each ridge match. **g**, Four arms of d. **h**, Calibration of the Fig. 4e logistic and normal residual risk maps. Points, estimates. Bars, paired participant-within-fold bootstrap 95% intervals (1,000 draws). Open circles, references. n, ≥1,880 development people, five-fold cross-validated (c, ≥160 below 12 g/dL). No hypothesis tests were run. With retina and age alone, ridge on raw retinal features was more accurate for six of nine values, and with the panel hidden for haemoglobin and haematocrit (e). Every ridge AUROC point estimate exceeded its BRAN setting (f), Ridge was more accurate below 12 g/dL without retina (c), and no completed arm exceeded the classifier without blood count input (d). With the normal residual map BRAN with retina and its ridge analogue were too extreme and Retina and age over-predicted (h). Risk maps were not fully nested. AUROC, area under the receiver operating characteristic curve. CBC, complete blood count. MCV, MCH and MCHC, mean corpuscular volume, haemoglobin and haemoglobin concentration. RDW, red cell distribution width.</t>
+          <t>**Extended Data Fig. 5 | Linear and raw-feature comparators for blood count completion.** **a**, Mean absolute error (MAE) relative to the training median, whole panel hidden. **b**, BRAN without retina minus ridge MAE, as a percentage of median MAE. **c**, Haemoglobin MAE below 12 g/dL and paired differences. **d**, Macro AUROC over 25 conditions for one classifier given each arm's estimates, and prespecified paired differences (Bonferroni). **e**, BRAN minus ridge models given its inputs plus 64 retinal components. **f**, AUROC for haemoglobin below 12 g/dL beside each ridge match. **g**, Four arms of **d**. **h**, Calibration of the Fig. 4e logistic and normal residual risk maps. Points, estimates. Bars, paired participant-within-fold bootstrap 95% intervals (1,000 draws). Open circles, references. *n*, ≥1,880 development people, five-fold cross-validated (**c**, ≥160 below 12 g/dL). No hypothesis tests were run. With retina and age alone, ridge on raw retinal features was more accurate for six of nine values, and with the panel hidden for haemoglobin and haematocrit (**e**). Every ridge AUROC point estimate exceeded its BRAN setting (**f**), ridge was more accurate below 12 g/dL without retina (**c**), and no completed arm exceeded the classifier without blood count input (**d**). With the normal residual map BRAN with retina and its ridge analogue were too extreme and the retina and age arm over-predicted (**h**). Risk maps were not fully nested. AUROC, area under the receiver operating characteristic curve. CBC, complete blood count. Other abbreviations as in Fig. 1.</t>
         </is>
       </c>
     </row>
